--- a/docs/xlsx/jobs-2026-10-17.xlsx
+++ b/docs/xlsx/jobs-2026-10-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,60 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Executive Assistant to Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>Prep for Prep</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 66500.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/743eb34d3e7449cea1eebb88f16cc0aa-executive-assistant-to-chief-executive-officer-prep-for-prep-new-york</t>
+  </si>
+  <si>
+    <t>Sightline Institute Principal Director, Program Development</t>
+  </si>
+  <si>
+    <t>Clover Search Works</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 166000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/af546ac2b1404ee2a9d206795f0c8688-sightline-institute-principal-director-program-development-clover-search-works-seattle</t>
+  </si>
+  <si>
+    <t>Sponsorship Care &amp; Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Everknown</t>
+  </si>
+  <si>
+    <t>Plano, Texas</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Religion Spirituality, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3f317ffbebb498097aee71d32b2d9bc-sponsorship-care-engagement-coordinator-everknown-plano</t>
+  </si>
+  <si>
     <t>Vice President of Stage Production &amp; Operations</t>
   </si>
   <si>
@@ -47,9 +101,6 @@
   </si>
   <si>
     <t>Santa Barbara, California</t>
-  </si>
-  <si>
-    <t>Full Time</t>
   </si>
   <si>
     <t>USD 150000.00 - 200000.00/year</t>
@@ -540,7 +591,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -602,10 +653,82 @@
         <v>14</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-17.xlsx
+++ b/docs/xlsx/jobs-2026-10-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
   <si>
     <t>Title</t>
   </si>
@@ -59,6 +59,24 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/743eb34d3e7449cea1eebb88f16cc0aa-executive-assistant-to-chief-executive-officer-prep-for-prep-new-york</t>
+  </si>
+  <si>
+    <t>Managing Director, Develpoment</t>
+  </si>
+  <si>
+    <t>Roosevelt Institute</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 162000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26897bd95fa0492286cc188a14538046-managing-director-develpoment-roosevelt-institute-washington</t>
   </si>
   <si>
     <t>Sightline Institute Principal Director, Program Development</t>
@@ -591,7 +609,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -670,30 +688,30 @@
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>25</v>
@@ -720,6 +738,29 @@
       </c>
       <c r="H5" s="2" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -729,6 +770,7 @@
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
